--- a/exports/ABCAPITAL_full_report.xlsx
+++ b/exports/ABCAPITAL_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q77"/>
+  <dimension ref="A1:U77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>6.92</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44581.55208333334</v>
+        <v>44582.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>127.85</v>
+        <v>124.7</v>
       </c>
       <c r="I2" t="n">
         <v>126.3865295</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>11</v>
       </c>
       <c r="K2" t="n">
-        <v>-3.22</v>
+        <v>-5.6</v>
       </c>
       <c r="L2" t="n">
-        <v>6.21</v>
+        <v>7.15</v>
       </c>
       <c r="M2" t="n">
-        <v>0.78</v>
+        <v>0.82</v>
       </c>
       <c r="N2" t="n">
-        <v>3.47</v>
+        <v>3.56</v>
       </c>
       <c r="O2" t="n">
         <v>-0.15</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>8.34</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44636.55208333334</v>
+        <v>44637.38541666666</v>
       </c>
       <c r="H3" t="n">
-        <v>108.4</v>
+        <v>109.2</v>
       </c>
       <c r="I3" t="n">
         <v>108.6312504083893</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>54.16666666666666</v>
+        <v>55</v>
       </c>
       <c r="K3" t="n">
-        <v>13.07</v>
+        <v>12.43</v>
       </c>
       <c r="L3" t="n">
         <v>3.49</v>
@@ -621,7 +656,19 @@
         <v>0</v>
       </c>
       <c r="Q3" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>6.56</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>112.25</v>
+        <v>108.9</v>
       </c>
       <c r="I4" t="n">
         <v>110.8194018960464</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>33</v>
+        <v>33.16666666666666</v>
       </c>
       <c r="K4" t="n">
-        <v>2.79</v>
+        <v>-0.27</v>
       </c>
       <c r="L4" t="n">
         <v>3.48</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,22 +764,22 @@
         <v>9.93</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44678.38541666666</v>
+        <v>44678.55208333334</v>
       </c>
       <c r="H5" t="n">
-        <v>117.9</v>
+        <v>120.45</v>
       </c>
       <c r="I5" t="n">
         <v>118.060712462009</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>7.833333333333333</v>
+        <v>8</v>
       </c>
       <c r="K5" t="n">
-        <v>-8.26</v>
+        <v>-10.61</v>
       </c>
       <c r="L5" t="n">
-        <v>9.640000000000001</v>
+        <v>11.94</v>
       </c>
       <c r="M5" t="n">
         <v>1.01</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -762,22 +833,22 @@
         <v>8.609999999999999</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44685.38541666666</v>
+        <v>44685.55208333334</v>
       </c>
       <c r="H6" t="n">
-        <v>116.65</v>
+        <v>113.7</v>
       </c>
       <c r="I6" t="n">
         <v>114.1006248612056</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K6" t="n">
-        <v>-3.15</v>
+        <v>-5.6</v>
       </c>
       <c r="L6" t="n">
-        <v>4.03</v>
+        <v>6.19</v>
       </c>
       <c r="M6" t="n">
         <v>1.33</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>9.99</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44711.38541666666</v>
+        <v>44711.55208333334</v>
       </c>
       <c r="H7" t="n">
-        <v>102.15</v>
+        <v>104.75</v>
       </c>
       <c r="I7" t="n">
         <v>104.1600443055749</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K7" t="n">
-        <v>10.16</v>
+        <v>7.87</v>
       </c>
       <c r="L7" t="n">
         <v>3.39</v>
@@ -849,7 +932,19 @@
         <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,28 +971,28 @@
         <v>9.57</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44722.55208333334</v>
+        <v>44725.38541666666</v>
       </c>
       <c r="H8" t="n">
-        <v>100.5</v>
+        <v>96.15000000000001</v>
       </c>
       <c r="I8" t="n">
         <v>97.29861787075265</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>11</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K8" t="n">
-        <v>-4.06</v>
+        <v>-8.210000000000001</v>
       </c>
       <c r="L8" t="n">
-        <v>4.53</v>
+        <v>8.5</v>
       </c>
       <c r="M8" t="n">
         <v>1.11</v>
       </c>
       <c r="N8" t="n">
-        <v>3.58</v>
+        <v>5.22</v>
       </c>
       <c r="O8" t="n">
         <v>4.91</v>
@@ -906,7 +1001,19 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>7.81</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44753.38541666666</v>
+        <v>44753.55208333334</v>
       </c>
       <c r="H9" t="n">
-        <v>93.84999999999999</v>
+        <v>95</v>
       </c>
       <c r="I9" t="n">
         <v>94.18903924335218</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>28</v>
+        <v>28.16666666666667</v>
       </c>
       <c r="K9" t="n">
-        <v>2.39</v>
+        <v>1.2</v>
       </c>
       <c r="L9" t="n">
         <v>3.43</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>6.14</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>115.9</v>
+        <v>111.65</v>
       </c>
       <c r="I10" t="n">
         <v>113.8827450937698</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>73</v>
+        <v>73.83333333333333</v>
       </c>
       <c r="K10" t="n">
-        <v>22</v>
+        <v>17.53</v>
       </c>
       <c r="L10" t="n">
         <v>5</v>
@@ -1011,7 +1130,7 @@
         <v>4.74</v>
       </c>
       <c r="N10" t="n">
-        <v>3.06</v>
+        <v>3.62</v>
       </c>
       <c r="O10" t="n">
         <v>2.76</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -1047,19 +1178,19 @@
         <v>8.869999999999999</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44858.76041666666</v>
+        <v>44859.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>114.5</v>
+        <v>115.3</v>
       </c>
       <c r="I11" t="n">
         <v>115.2647304847278</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>31.375</v>
+        <v>32</v>
       </c>
       <c r="K11" t="n">
-        <v>-2.55</v>
+        <v>-3.27</v>
       </c>
       <c r="L11" t="n">
         <v>4.75</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>41</v>
+        <v>42</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.12</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44915.55208333334</v>
+        <v>44916.38541666666</v>
       </c>
       <c r="H12" t="n">
-        <v>153.25</v>
+        <v>151.3</v>
       </c>
       <c r="I12" t="n">
         <v>151.3307248361482</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>56.16666666666666</v>
+        <v>57</v>
       </c>
       <c r="K12" t="n">
-        <v>32.91</v>
+        <v>31.22</v>
       </c>
       <c r="L12" t="n">
         <v>2.08</v>
@@ -1125,7 +1268,7 @@
         <v>1.82</v>
       </c>
       <c r="N12" t="n">
-        <v>2.77</v>
+        <v>2.94</v>
       </c>
       <c r="O12" t="n">
         <v>1.05</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="13">
@@ -1161,22 +1316,22 @@
         <v>7.61</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44928.38541666666</v>
+        <v>44928.55208333334</v>
       </c>
       <c r="H13" t="n">
-        <v>153.2</v>
+        <v>155.8</v>
       </c>
       <c r="I13" t="n">
         <v>153.9074912400536</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>12</v>
+        <v>12.16666666666667</v>
       </c>
       <c r="K13" t="n">
-        <v>-1.26</v>
+        <v>-2.97</v>
       </c>
       <c r="L13" t="n">
-        <v>2.78</v>
+        <v>3.11</v>
       </c>
       <c r="M13" t="n">
         <v>0.75</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,22 +1385,22 @@
         <v>6.67</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44931.55208333334</v>
+        <v>44932.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>149.6</v>
+        <v>145.4</v>
       </c>
       <c r="I14" t="n">
         <v>145.5776268840938</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3</v>
+        <v>3.833333333333333</v>
       </c>
       <c r="K14" t="n">
-        <v>-3.98</v>
+        <v>-6.68</v>
       </c>
       <c r="L14" t="n">
-        <v>5.68</v>
+        <v>6.87</v>
       </c>
       <c r="M14" t="n">
         <v>0.03</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S14" t="b">
+        <v>0</v>
+      </c>
+      <c r="T14" t="n">
+        <v>1</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -1275,19 +1454,19 @@
         <v>8.59</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44960.55208333334</v>
+        <v>44963.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>142</v>
+        <v>145.1</v>
       </c>
       <c r="I15" t="n">
         <v>143.1318722279471</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>28.16666666666667</v>
+        <v>31</v>
       </c>
       <c r="K15" t="n">
-        <v>2.34</v>
+        <v>0.21</v>
       </c>
       <c r="L15" t="n">
         <v>3.44</v>
@@ -1296,7 +1475,7 @@
         <v>4.45</v>
       </c>
       <c r="N15" t="n">
-        <v>2.53</v>
+        <v>2.68</v>
       </c>
       <c r="O15" t="n">
         <v>-3.11</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44951</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>9.52</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44978.55208333334</v>
+        <v>44979.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>143</v>
+        <v>139.25</v>
       </c>
       <c r="I16" t="n">
         <v>139.3648397613368</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.45</v>
+        <v>-4.03</v>
       </c>
       <c r="L16" t="n">
-        <v>2.89</v>
+        <v>4.34</v>
       </c>
       <c r="M16" t="n">
         <v>1.02</v>
       </c>
       <c r="N16" t="n">
-        <v>1.81</v>
+        <v>2.48</v>
       </c>
       <c r="O16" t="n">
         <v>2.68</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>0</v>
+      </c>
+      <c r="T16" t="n">
+        <v>1</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1389,28 +1592,28 @@
         <v>6.49</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>44985.55208333334</v>
+        <v>44986.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>145.95</v>
+        <v>151.1</v>
       </c>
       <c r="I17" t="n">
         <v>146.3268025065903</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K17" t="n">
-        <v>-4.81</v>
+        <v>-8.51</v>
       </c>
       <c r="L17" t="n">
-        <v>5.46</v>
+        <v>9.01</v>
       </c>
       <c r="M17" t="n">
         <v>0.07000000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>3.18</v>
+        <v>4.49</v>
       </c>
       <c r="O17" t="n">
         <v>-2.48</v>
@@ -1419,7 +1622,19 @@
         <v>0</v>
       </c>
       <c r="Q17" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.6</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>154</v>
+        <v>150.15</v>
       </c>
       <c r="I18" t="n">
         <v>150.2536517742311</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>12</v>
       </c>
       <c r="K18" t="n">
-        <v>1.92</v>
+        <v>-0.63</v>
       </c>
       <c r="L18" t="n">
         <v>3.81</v>
@@ -1467,7 +1682,7 @@
         <v>0.83</v>
       </c>
       <c r="N18" t="n">
-        <v>1.6</v>
+        <v>4.42</v>
       </c>
       <c r="O18" t="n">
         <v>4.49</v>
@@ -1476,7 +1691,19 @@
         <v>1</v>
       </c>
       <c r="Q18" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S18" t="b">
+        <v>0</v>
+      </c>
+      <c r="T18" t="n">
+        <v>1</v>
+      </c>
+      <c r="U18" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>6.8</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45002.38541666666</v>
+        <v>45002.55208333334</v>
       </c>
       <c r="H19" t="n">
-        <v>153.1</v>
+        <v>154.45</v>
       </c>
       <c r="I19" t="n">
         <v>153.3769237927058</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.96</v>
+        <v>-2.86</v>
       </c>
       <c r="L19" t="n">
         <v>3.1</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,28 +1799,28 @@
         <v>6.69</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45008.55208333334</v>
+        <v>45009.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>153.7</v>
+        <v>146.3</v>
       </c>
       <c r="I20" t="n">
         <v>146.6558352507682</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.49</v>
+        <v>-5.28</v>
       </c>
       <c r="L20" t="n">
-        <v>4.27</v>
+        <v>6.22</v>
       </c>
       <c r="M20" t="n">
-        <v>0.03</v>
+        <v>0.59</v>
       </c>
       <c r="N20" t="n">
-        <v>2.65</v>
+        <v>6.83</v>
       </c>
       <c r="O20" t="n">
         <v>3.62</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S20" t="b">
+        <v>0</v>
+      </c>
+      <c r="T20" t="n">
+        <v>1</v>
+      </c>
+      <c r="U20" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="21">
@@ -1617,22 +1868,22 @@
         <v>9.32</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45019.55208333334</v>
+        <v>45021.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>153.9</v>
+        <v>156</v>
       </c>
       <c r="I21" t="n">
         <v>155.3273818427739</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>10.16666666666667</v>
+        <v>12</v>
       </c>
       <c r="K21" t="n">
-        <v>-5.19</v>
+        <v>-6.63</v>
       </c>
       <c r="L21" t="n">
-        <v>6.08</v>
+        <v>6.94</v>
       </c>
       <c r="M21" t="n">
         <v>0.72</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>2</v>
+      </c>
+      <c r="U21" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>7.63</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45057.38541666666</v>
+        <v>45057.55208333334</v>
       </c>
       <c r="H22" t="n">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="I22" t="n">
         <v>165.1512194486168</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K22" t="n">
-        <v>10.26</v>
+        <v>5.13</v>
       </c>
       <c r="L22" t="n">
         <v>2.05</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>47</v>
+        <v>48</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,25 +2006,25 @@
         <v>9.300000000000001</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45078.55208333334</v>
+        <v>45079.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>171.5</v>
+        <v>172.95</v>
       </c>
       <c r="I23" t="n">
         <v>172.110860838823</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>21</v>
+        <v>21.83333333333333</v>
       </c>
       <c r="K23" t="n">
-        <v>-4.57</v>
+        <v>-5.46</v>
       </c>
       <c r="L23" t="n">
-        <v>5.64</v>
+        <v>7.68</v>
       </c>
       <c r="M23" t="n">
-        <v>1.1</v>
+        <v>1.6</v>
       </c>
       <c r="N23" t="n">
         <v>3.41</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45071</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,19 +2075,19 @@
         <v>4.11</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45098.55208333334</v>
+        <v>45099.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>179.8</v>
+        <v>172.15</v>
       </c>
       <c r="I24" t="n">
         <v>173.3411887851852</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K24" t="n">
-        <v>3.96</v>
+        <v>-0.46</v>
       </c>
       <c r="L24" t="n">
         <v>3.24</v>
@@ -1809,7 +2096,7 @@
         <v>0.31</v>
       </c>
       <c r="N24" t="n">
-        <v>2.26</v>
+        <v>4.59</v>
       </c>
       <c r="O24" t="n">
         <v>0.67</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S24" t="b">
+        <v>0</v>
+      </c>
+      <c r="T24" t="n">
+        <v>1</v>
+      </c>
+      <c r="U24" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>7.99</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45103.38541666666</v>
+        <v>45103.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>174.75</v>
+        <v>182</v>
       </c>
       <c r="I25" t="n">
         <v>180.31871103804</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-1.51</v>
+        <v>-5.72</v>
       </c>
       <c r="L25" t="n">
-        <v>4.85</v>
+        <v>5.72</v>
       </c>
       <c r="M25" t="n">
         <v>0.28</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,19 +2213,19 @@
         <v>8.4</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45139.55208333334</v>
+        <v>45140.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>195.4</v>
+        <v>185.25</v>
       </c>
       <c r="I26" t="n">
         <v>188.5511097319336</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>7.36</v>
+        <v>1.79</v>
       </c>
       <c r="L26" t="n">
         <v>4.01</v>
@@ -1923,7 +2234,7 @@
         <v>0.41</v>
       </c>
       <c r="N26" t="n">
-        <v>2.35</v>
+        <v>2.89</v>
       </c>
       <c r="O26" t="n">
         <v>3.73</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45105</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>7.87</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45170.55208333334</v>
+        <v>45173.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>184.6</v>
+        <v>189.6</v>
       </c>
       <c r="I27" t="n">
         <v>187.7544418067748</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>30.16666666666667</v>
+        <v>33</v>
       </c>
       <c r="K27" t="n">
-        <v>0.35</v>
+        <v>-2.35</v>
       </c>
       <c r="L27" t="n">
         <v>5.48</v>
@@ -1980,7 +2303,7 @@
         <v>1.04</v>
       </c>
       <c r="N27" t="n">
-        <v>1.85</v>
+        <v>3.22</v>
       </c>
       <c r="O27" t="n">
         <v>-2.89</v>
@@ -1989,7 +2312,19 @@
         <v>0</v>
       </c>
       <c r="Q27" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>2</v>
+      </c>
+      <c r="U27" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="28">
@@ -2016,22 +2351,22 @@
         <v>6.66</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45181.38541666666</v>
+        <v>45181.55208333334</v>
       </c>
       <c r="H28" t="n">
-        <v>182.25</v>
+        <v>180.5</v>
       </c>
       <c r="I28" t="n">
         <v>182.163781033094</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>8</v>
+        <v>8.166666666666666</v>
       </c>
       <c r="K28" t="n">
-        <v>-3.88</v>
+        <v>-4.8</v>
       </c>
       <c r="L28" t="n">
-        <v>4.4</v>
+        <v>4.91</v>
       </c>
       <c r="M28" t="n">
         <v>0.43</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S28" t="b">
+        <v>0</v>
+      </c>
+      <c r="T28" t="n">
+        <v>1</v>
+      </c>
+      <c r="U28" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -2073,19 +2420,19 @@
         <v>6.49</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45217.55208333334</v>
+        <v>45218.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>181</v>
+        <v>184.65</v>
       </c>
       <c r="I29" t="n">
         <v>183.5927489886323</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K29" t="n">
-        <v>-0.28</v>
+        <v>-2.3</v>
       </c>
       <c r="L29" t="n">
         <v>3.24</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>49</v>
+        <v>50</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,28 +2489,28 @@
         <v>6.84</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>181.3</v>
+        <v>175</v>
       </c>
       <c r="I30" t="n">
         <v>175.4674233881542</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.81</v>
+        <v>-5.23</v>
       </c>
       <c r="L30" t="n">
-        <v>3.79</v>
+        <v>5.36</v>
       </c>
       <c r="M30" t="n">
         <v>1.27</v>
       </c>
       <c r="N30" t="n">
-        <v>1.39</v>
+        <v>4.94</v>
       </c>
       <c r="O30" t="n">
         <v>1.57</v>
@@ -2160,7 +2519,19 @@
         <v>0</v>
       </c>
       <c r="Q30" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,28 +2558,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45243.55208333334</v>
+        <v>45245.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>178</v>
+        <v>182.2</v>
       </c>
       <c r="I31" t="n">
         <v>179.5138540983081</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K31" t="n">
-        <v>-1.71</v>
+        <v>-4.11</v>
       </c>
       <c r="L31" t="n">
         <v>4.57</v>
       </c>
       <c r="M31" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="N31" t="n">
-        <v>2.07</v>
+        <v>2.13</v>
       </c>
       <c r="O31" t="n">
         <v>-4.94</v>
@@ -2217,7 +2588,19 @@
         <v>1</v>
       </c>
       <c r="Q31" t="n">
-        <v>31</v>
+        <v>32</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,28 +2627,28 @@
         <v>5.34</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45246.55208333334</v>
+        <v>45247.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>181.2</v>
+        <v>171.15</v>
       </c>
       <c r="I32" t="n">
         <v>174.3298171032323</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.55</v>
+        <v>-6.06</v>
       </c>
       <c r="L32" t="n">
-        <v>2.06</v>
+        <v>7.46</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>3.42</v>
       </c>
       <c r="N32" t="n">
-        <v>0.33</v>
+        <v>5.63</v>
       </c>
       <c r="O32" t="n">
         <v>2.13</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>6.46</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45289.38541666666</v>
+        <v>45289.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>165.6</v>
+        <v>166</v>
       </c>
       <c r="I33" t="n">
         <v>165.9295731128209</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>42</v>
+        <v>42.16666666666666</v>
       </c>
       <c r="K33" t="n">
-        <v>3.24</v>
+        <v>3.01</v>
       </c>
       <c r="L33" t="n">
         <v>2.48</v>
@@ -2331,7 +2726,19 @@
         <v>1</v>
       </c>
       <c r="Q33" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>3</v>
+      </c>
+      <c r="U33" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>4.49</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45311.55208333334</v>
+        <v>45314.38541666666</v>
       </c>
       <c r="H34" t="n">
-        <v>174.45</v>
+        <v>166.2</v>
       </c>
       <c r="I34" t="n">
         <v>171.0201185581079</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>22</v>
+        <v>24.83333333333333</v>
       </c>
       <c r="K34" t="n">
-        <v>5.09</v>
+        <v>0.12</v>
       </c>
       <c r="L34" t="n">
         <v>0.96</v>
@@ -2379,7 +2786,7 @@
         <v>1.09</v>
       </c>
       <c r="N34" t="n">
-        <v>1.82</v>
+        <v>5.76</v>
       </c>
       <c r="O34" t="n">
         <v>2.6</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="35">
@@ -2415,28 +2834,28 @@
         <v>8.44</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45323.55208333334</v>
+        <v>45324.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>167</v>
+        <v>180.25</v>
       </c>
       <c r="I35" t="n">
         <v>174.0364842700519</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K35" t="n">
-        <v>-0.48</v>
+        <v>-8.449999999999999</v>
       </c>
       <c r="L35" t="n">
-        <v>5.48</v>
+        <v>11.55</v>
       </c>
       <c r="M35" t="n">
-        <v>0.92</v>
+        <v>1.2</v>
       </c>
       <c r="N35" t="n">
-        <v>1.81</v>
+        <v>7.78</v>
       </c>
       <c r="O35" t="n">
         <v>-5.76</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.4</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45356.55208333334</v>
+        <v>45357.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>192</v>
+        <v>176.95</v>
       </c>
       <c r="I36" t="n">
         <v>180.4028860651487</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>32.16666666666666</v>
+        <v>33</v>
       </c>
       <c r="K36" t="n">
-        <v>6.52</v>
+        <v>-1.83</v>
       </c>
       <c r="L36" t="n">
         <v>6.24</v>
@@ -2493,7 +2924,7 @@
         <v>1.22</v>
       </c>
       <c r="N36" t="n">
-        <v>4.36</v>
+        <v>5.7</v>
       </c>
       <c r="O36" t="n">
         <v>7.78</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,28 +2972,28 @@
         <v>12.56</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45383.55208333334</v>
+        <v>45384.38541666666</v>
       </c>
       <c r="H37" t="n">
-        <v>181.9</v>
+        <v>197.8</v>
       </c>
       <c r="I37" t="n">
         <v>182.3814931073142</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.8</v>
+        <v>-11.78</v>
       </c>
       <c r="L37" t="n">
-        <v>8.67</v>
+        <v>12.8</v>
       </c>
       <c r="M37" t="n">
-        <v>2.75</v>
+        <v>3.35</v>
       </c>
       <c r="N37" t="n">
-        <v>3.35</v>
+        <v>10.47</v>
       </c>
       <c r="O37" t="n">
         <v>-5.7</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,19 +3041,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45418.55208333334</v>
+        <v>45419.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>226.85</v>
+        <v>216.05</v>
       </c>
       <c r="I38" t="n">
         <v>221.2366632312002</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K38" t="n">
-        <v>14.69</v>
+        <v>9.23</v>
       </c>
       <c r="L38" t="n">
         <v>5.97</v>
@@ -2616,7 +3071,19 @@
         <v>1</v>
       </c>
       <c r="Q38" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S38" t="b">
+        <v>1</v>
+      </c>
+      <c r="T38" t="n">
+        <v>2</v>
+      </c>
+      <c r="U38" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="39">
@@ -2643,19 +3110,19 @@
         <v>10.61</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45436.38541666666</v>
+        <v>45436.55208333334</v>
       </c>
       <c r="H39" t="n">
-        <v>229.3</v>
+        <v>230.25</v>
       </c>
       <c r="I39" t="n">
         <v>229.4323096956958</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>17</v>
+        <v>17.16666666666667</v>
       </c>
       <c r="K39" t="n">
-        <v>-6.13</v>
+        <v>-6.57</v>
       </c>
       <c r="L39" t="n">
         <v>6.97</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.61</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>229.5</v>
+        <v>210.05</v>
       </c>
       <c r="I40" t="n">
         <v>216.678025040653</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>10</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="K40" t="n">
-        <v>-0.33</v>
+        <v>-8.77</v>
       </c>
       <c r="L40" t="n">
-        <v>4.34</v>
+        <v>15.09</v>
       </c>
       <c r="M40" t="n">
         <v>0.44</v>
       </c>
       <c r="N40" t="n">
-        <v>1.86</v>
+        <v>10.24</v>
       </c>
       <c r="O40" t="n">
         <v>1.43</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45442</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.07</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>231.6</v>
+        <v>234.2</v>
       </c>
       <c r="I41" t="n">
         <v>233.7405545017475</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K41" t="n">
-        <v>-10.26</v>
+        <v>-11.5</v>
       </c>
       <c r="L41" t="n">
         <v>13.02</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,19 +3317,19 @@
         <v>10.59</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45484.38541666666</v>
+        <v>45484.55208333334</v>
       </c>
       <c r="H42" t="n">
-        <v>226.94</v>
+        <v>226.66</v>
       </c>
       <c r="I42" t="n">
         <v>226.9155518673678</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K42" t="n">
-        <v>-3.1</v>
+        <v>-3.22</v>
       </c>
       <c r="L42" t="n">
         <v>4.14</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S42" t="b">
+        <v>1</v>
+      </c>
+      <c r="T42" t="n">
+        <v>2</v>
+      </c>
+      <c r="U42" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>4.7</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45503.55208333334</v>
+        <v>45504.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>222.8</v>
+        <v>226.5</v>
       </c>
       <c r="I43" t="n">
         <v>225.5307159365002</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>19</v>
+        <v>19.83333333333333</v>
       </c>
       <c r="K43" t="n">
-        <v>1.7</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="L43" t="n">
         <v>0.92</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="44">
@@ -2928,28 +3455,28 @@
         <v>5.36</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45505.55208333334</v>
+        <v>45506.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>219.95</v>
+        <v>214.9</v>
       </c>
       <c r="I44" t="n">
         <v>216.0414859722775</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K44" t="n">
-        <v>-2.89</v>
+        <v>-5.12</v>
       </c>
       <c r="L44" t="n">
-        <v>4</v>
+        <v>8.17</v>
       </c>
       <c r="M44" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="N44" t="n">
-        <v>3.11</v>
+        <v>3.93</v>
       </c>
       <c r="O44" t="n">
         <v>1.89</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S44" t="b">
+        <v>0</v>
+      </c>
+      <c r="T44" t="n">
+        <v>1</v>
+      </c>
+      <c r="U44" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -2985,22 +3524,22 @@
         <v>6.07</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45524.55208333334</v>
+        <v>45525.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>218.28</v>
+        <v>222.6</v>
       </c>
       <c r="I45" t="n">
         <v>220.1618628119719</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>18.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.57</v>
+        <v>-3.58</v>
       </c>
       <c r="L45" t="n">
-        <v>2.19</v>
+        <v>4.39</v>
       </c>
       <c r="M45" t="n">
         <v>1.38</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,22 +3593,22 @@
         <v>7.25</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>216.5</v>
+        <v>215.86</v>
       </c>
       <c r="I46" t="n">
         <v>215.983603051269</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>19</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.74</v>
+        <v>-3.03</v>
       </c>
       <c r="L46" t="n">
-        <v>3.13</v>
+        <v>4.02</v>
       </c>
       <c r="M46" t="n">
         <v>2.08</v>
@@ -3072,7 +3623,19 @@
         <v>0</v>
       </c>
       <c r="Q46" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,22 +3662,22 @@
         <v>5.07</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45548.38541666666</v>
+        <v>45548.55208333334</v>
       </c>
       <c r="H47" t="n">
-        <v>225.68</v>
+        <v>226.4</v>
       </c>
       <c r="I47" t="n">
         <v>225.747417890421</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>4</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K47" t="n">
-        <v>-4.55</v>
+        <v>-4.88</v>
       </c>
       <c r="L47" t="n">
-        <v>4.63</v>
+        <v>5.24</v>
       </c>
       <c r="M47" t="n">
         <v>0.86</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,19 +3731,19 @@
         <v>5.37</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45569.38541666666</v>
+        <v>45569.55208333334</v>
       </c>
       <c r="H48" t="n">
-        <v>230.09</v>
+        <v>228</v>
       </c>
       <c r="I48" t="n">
         <v>228.6193899322336</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>20.83333333333333</v>
+        <v>21</v>
       </c>
       <c r="K48" t="n">
-        <v>1.63</v>
+        <v>0.71</v>
       </c>
       <c r="L48" t="n">
         <v>1.57</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>6.42</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45628.55208333334</v>
+        <v>45629.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>194.25</v>
+        <v>197.33</v>
       </c>
       <c r="I49" t="n">
         <v>195.4863741646398</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>59</v>
+        <v>59.83333333333334</v>
       </c>
       <c r="K49" t="n">
-        <v>14.8</v>
+        <v>13.45</v>
       </c>
       <c r="L49" t="n">
         <v>2.44</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>78</v>
+        <v>79</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>3</v>
+      </c>
+      <c r="U49" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>5.13</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45642.55208333334</v>
+        <v>45643.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>196.01</v>
+        <v>193.63</v>
       </c>
       <c r="I50" t="n">
         <v>193.6372794709516</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K50" t="n">
-        <v>-0.67</v>
+        <v>-1.88</v>
       </c>
       <c r="L50" t="n">
         <v>3.03</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S50" t="b">
+        <v>0</v>
+      </c>
+      <c r="T50" t="n">
+        <v>1</v>
+      </c>
+      <c r="U50" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -3327,19 +3938,19 @@
         <v>5.72</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45659.55208333334</v>
+        <v>45660.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>183.55</v>
+        <v>185.85</v>
       </c>
       <c r="I51" t="n">
         <v>185.7380730831125</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K51" t="n">
-        <v>5.21</v>
+        <v>4.02</v>
       </c>
       <c r="L51" t="n">
         <v>2.05</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,22 +4007,22 @@
         <v>4.79</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45663.38541666666</v>
+        <v>45663.55208333334</v>
       </c>
       <c r="H52" t="n">
-        <v>178.15</v>
+        <v>176.4</v>
       </c>
       <c r="I52" t="n">
         <v>177.2731316251529</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.14</v>
+        <v>-5.08</v>
       </c>
       <c r="L52" t="n">
-        <v>5.19</v>
+        <v>5.69</v>
       </c>
       <c r="M52" t="n">
         <v>-0</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>3</v>
+        <v>4</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>5.7</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45686.55208333334</v>
+        <v>45687.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>176.23</v>
+        <v>177.25</v>
       </c>
       <c r="I53" t="n">
         <v>176.6045690834474</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>23</v>
+        <v>23.83333333333333</v>
       </c>
       <c r="K53" t="n">
-        <v>0.1</v>
+        <v>-0.48</v>
       </c>
       <c r="L53" t="n">
         <v>2.24</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S53" t="b">
+        <v>0</v>
+      </c>
+      <c r="T53" t="n">
+        <v>1</v>
+      </c>
+      <c r="U53" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -3498,22 +4145,22 @@
         <v>7.24</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45691.55208333334</v>
+        <v>45692.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>169.12</v>
+        <v>167.25</v>
       </c>
       <c r="I54" t="n">
         <v>168.3843722480961</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K54" t="n">
-        <v>-4.59</v>
+        <v>-5.64</v>
       </c>
       <c r="L54" t="n">
-        <v>4.82</v>
+        <v>6.49</v>
       </c>
       <c r="M54" t="n">
         <v>0.57</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S54" t="b">
+        <v>0</v>
+      </c>
+      <c r="T54" t="n">
+        <v>1</v>
+      </c>
+      <c r="U54" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>10.63</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45728.38541666666</v>
+        <v>45728.55208333334</v>
       </c>
       <c r="H55" t="n">
-        <v>161.62</v>
+        <v>162.95</v>
       </c>
       <c r="I55" t="n">
         <v>162.4802424039677</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>36</v>
+        <v>36.16666666666666</v>
       </c>
       <c r="K55" t="n">
-        <v>3.37</v>
+        <v>2.57</v>
       </c>
       <c r="L55" t="n">
         <v>3.79</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S55" t="b">
+        <v>1</v>
+      </c>
+      <c r="T55" t="n">
+        <v>2</v>
+      </c>
+      <c r="U55" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>6.73</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45751.55208333334</v>
+        <v>45754.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>188.95</v>
+        <v>177.01</v>
       </c>
       <c r="I56" t="n">
         <v>179.9567764914819</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>23</v>
+        <v>25.83333333333333</v>
       </c>
       <c r="K56" t="n">
-        <v>15.96</v>
+        <v>8.630000000000001</v>
       </c>
       <c r="L56" t="n">
         <v>1.45</v>
       </c>
       <c r="M56" t="n">
-        <v>1.04</v>
+        <v>10.33</v>
       </c>
       <c r="N56" t="n">
-        <v>2.19</v>
+        <v>4.21</v>
       </c>
       <c r="O56" t="n">
         <v>2.74</v>
@@ -3642,7 +4313,19 @@
         <v>0</v>
       </c>
       <c r="Q56" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>8.699999999999999</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45762.55208333334</v>
+        <v>45763.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>190.67</v>
+        <v>195.15</v>
       </c>
       <c r="I57" t="n">
         <v>192.4057899377097</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K57" t="n">
-        <v>-7.72</v>
+        <v>-10.25</v>
       </c>
       <c r="L57" t="n">
-        <v>7.9</v>
+        <v>10.36</v>
       </c>
       <c r="M57" t="n">
         <v>1.57</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S57" t="b">
+        <v>0</v>
+      </c>
+      <c r="T57" t="n">
+        <v>1</v>
+      </c>
+      <c r="U57" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>8.57</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45783.38541666666</v>
+        <v>45783.55208333334</v>
       </c>
       <c r="H58" t="n">
-        <v>195.09</v>
+        <v>191.9</v>
       </c>
       <c r="I58" t="n">
         <v>194.2963809388727</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>20</v>
+        <v>20.16666666666667</v>
       </c>
       <c r="K58" t="n">
-        <v>-0.03</v>
+        <v>-1.67</v>
       </c>
       <c r="L58" t="n">
         <v>2.59</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,22 +4490,22 @@
         <v>6.95</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45789.55208333334</v>
+        <v>45790.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>205.02</v>
+        <v>207.46</v>
       </c>
       <c r="I59" t="n">
         <v>205.2416828197209</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K59" t="n">
-        <v>-6.84</v>
+        <v>-8.109999999999999</v>
       </c>
       <c r="L59" t="n">
-        <v>7.34</v>
+        <v>9.48</v>
       </c>
       <c r="M59" t="n">
         <v>2.45</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S59" t="b">
+        <v>0</v>
+      </c>
+      <c r="T59" t="n">
+        <v>1</v>
+      </c>
+      <c r="U59" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>8.58</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45855.55208333334</v>
+        <v>45856.38541666666</v>
       </c>
       <c r="H60" t="n">
-        <v>267.6</v>
+        <v>265.25</v>
       </c>
       <c r="I60" t="n">
         <v>266.5252010617326</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>65.16666666666667</v>
+        <v>66</v>
       </c>
       <c r="K60" t="n">
-        <v>28.99</v>
+        <v>27.86</v>
       </c>
       <c r="L60" t="n">
         <v>3.02</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>4.8</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45870.55208333334</v>
+        <v>45873.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>250.05</v>
+        <v>262.75</v>
       </c>
       <c r="I61" t="n">
         <v>261.4407980626013</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K61" t="n">
-        <v>5.73</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="L61" t="n">
         <v>3.2</v>
       </c>
       <c r="M61" t="n">
-        <v>0.34</v>
+        <v>0.58</v>
       </c>
       <c r="N61" t="n">
-        <v>3.1</v>
+        <v>11.9</v>
       </c>
       <c r="O61" t="n">
         <v>-1.31</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,19 +4697,19 @@
         <v>8.66</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45926.38541666666</v>
+        <v>45926.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>283.2</v>
+        <v>280.25</v>
       </c>
       <c r="I62" t="n">
         <v>280.7943730300592</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>53</v>
+        <v>53.16666666666666</v>
       </c>
       <c r="K62" t="n">
-        <v>7.78</v>
+        <v>6.66</v>
       </c>
       <c r="L62" t="n">
         <v>4.28</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>75</v>
+        <v>76</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="63">
@@ -4011,22 +4766,22 @@
         <v>5.51</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45931.38541666666</v>
+        <v>45931.55208333334</v>
       </c>
       <c r="H63" t="n">
-        <v>292.65</v>
+        <v>301</v>
       </c>
       <c r="I63" t="n">
         <v>295.6944071694803</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.833333333333333</v>
+        <v>5</v>
       </c>
       <c r="K63" t="n">
-        <v>-4.42</v>
+        <v>-7.4</v>
       </c>
       <c r="L63" t="n">
-        <v>5.19</v>
+        <v>7.62</v>
       </c>
       <c r="M63" t="n">
         <v>0.47</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>7.16</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46007.38541666666</v>
+        <v>46007.55208333334</v>
       </c>
       <c r="H64" t="n">
-        <v>350.35</v>
+        <v>346.85</v>
       </c>
       <c r="I64" t="n">
         <v>347.9925109738963</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>75.83333333333333</v>
+        <v>76</v>
       </c>
       <c r="K64" t="n">
-        <v>16.4</v>
+        <v>15.23</v>
       </c>
       <c r="L64" t="n">
         <v>3.69</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>3</v>
+      </c>
+      <c r="U64" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>5.28</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>46023.38541666666</v>
+        <v>46023.55208333334</v>
       </c>
       <c r="H65" t="n">
-        <v>359.75</v>
+        <v>362</v>
       </c>
       <c r="I65" t="n">
         <v>361.3017849288636</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>15.83333333333333</v>
+        <v>16</v>
       </c>
       <c r="K65" t="n">
-        <v>-3.72</v>
+        <v>-4.37</v>
       </c>
       <c r="L65" t="n">
-        <v>4.15</v>
+        <v>4.58</v>
       </c>
       <c r="M65" t="n">
         <v>0.8</v>
@@ -4155,7 +4934,19 @@
         <v>0</v>
       </c>
       <c r="Q65" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>4.62</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>46043.38541666666</v>
+        <v>46043.55208333334</v>
       </c>
       <c r="H66" t="n">
-        <v>351.4</v>
+        <v>346</v>
       </c>
       <c r="I66" t="n">
         <v>350.2193037936041</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>19.83333333333333</v>
+        <v>20</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.93</v>
+        <v>-4.42</v>
       </c>
       <c r="L66" t="n">
         <v>5.22</v>
@@ -4212,7 +5003,19 @@
         <v>0</v>
       </c>
       <c r="Q66" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>7.09</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>46059.55208333334</v>
+        <v>46062.38541666666</v>
       </c>
       <c r="H67" t="n">
-        <v>346</v>
+        <v>351.55</v>
       </c>
       <c r="I67" t="n">
         <v>349.6667739894744</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>16</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K67" t="n">
-        <v>0</v>
+        <v>-1.6</v>
       </c>
       <c r="L67" t="n">
         <v>4.29</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>2</v>
+      </c>
+      <c r="U67" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>8.59</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>46083.55208333334</v>
+        <v>46085.38541666666</v>
       </c>
       <c r="H68" t="n">
-        <v>338.25</v>
+        <v>323.1</v>
       </c>
       <c r="I68" t="n">
         <v>334.7764458267076</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>23</v>
       </c>
       <c r="K68" t="n">
-        <v>-3.78</v>
+        <v>-8.09</v>
       </c>
       <c r="L68" t="n">
-        <v>5.82</v>
+        <v>9.289999999999999</v>
       </c>
       <c r="M68" t="n">
         <v>2.13</v>
       </c>
       <c r="N68" t="n">
-        <v>3.88</v>
+        <v>5.28</v>
       </c>
       <c r="O68" t="n">
         <v>1.95</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,28 +5180,28 @@
         <v>9.68</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H69" t="n">
-        <v>307</v>
+        <v>335.95</v>
       </c>
       <c r="I69" t="n">
         <v>318.2380450338708</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>34.16666666666666</v>
+        <v>35</v>
       </c>
       <c r="K69" t="n">
-        <v>4.98</v>
+        <v>-3.98</v>
       </c>
       <c r="L69" t="n">
         <v>4.67</v>
       </c>
       <c r="M69" t="n">
-        <v>2.47</v>
+        <v>5.44</v>
       </c>
       <c r="N69" t="n">
-        <v>4.16</v>
+        <v>10.23</v>
       </c>
       <c r="O69" t="n">
         <v>-5.28</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.38</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>46153.55208333334</v>
+        <v>46154.38541666666</v>
       </c>
       <c r="H70" t="n">
-        <v>353.65</v>
+        <v>345.5</v>
       </c>
       <c r="I70" t="n">
         <v>346.4420500549328</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>33.16666666666666</v>
+        <v>34</v>
       </c>
       <c r="K70" t="n">
-        <v>5.27</v>
+        <v>2.84</v>
       </c>
       <c r="L70" t="n">
         <v>4.45</v>
@@ -4431,7 +5270,7 @@
         <v>3.47</v>
       </c>
       <c r="N70" t="n">
-        <v>2.54</v>
+        <v>3.58</v>
       </c>
       <c r="O70" t="n">
         <v>10.23</v>
@@ -4440,7 +5279,19 @@
         <v>1</v>
       </c>
       <c r="Q70" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>2</v>
+      </c>
+      <c r="U70" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>7.98</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>46185.38541666666</v>
+        <v>46185.55208333334</v>
       </c>
       <c r="H71" t="n">
-        <v>346</v>
+        <v>357.35</v>
       </c>
       <c r="I71" t="n">
         <v>357.0187890240917</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>31</v>
+        <v>31.16666666666667</v>
       </c>
       <c r="K71" t="n">
-        <v>-0.14</v>
+        <v>-3.43</v>
       </c>
       <c r="L71" t="n">
         <v>7.03</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>2</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>7.91</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>46211.38541666666</v>
+        <v>46211.55208333334</v>
       </c>
       <c r="H72" t="n">
-        <v>401.95</v>
+        <v>387.6</v>
       </c>
       <c r="I72" t="n">
         <v>389.8287414515168</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>25.83333333333333</v>
+        <v>26</v>
       </c>
       <c r="K72" t="n">
-        <v>12.48</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="L72" t="n">
         <v>3.23</v>
@@ -4554,7 +5417,19 @@
         <v>1</v>
       </c>
       <c r="Q72" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>2</v>
+      </c>
+      <c r="U72" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>7.31</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46233.55208333334</v>
+        <v>46234.38541666666</v>
       </c>
       <c r="H73" t="n">
-        <v>394</v>
+        <v>410</v>
       </c>
       <c r="I73" t="n">
         <v>409.0064988336214</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>22</v>
+        <v>22.83333333333333</v>
       </c>
       <c r="K73" t="n">
-        <v>-1.65</v>
+        <v>-5.78</v>
       </c>
       <c r="L73" t="n">
         <v>6.14</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>2</v>
+      </c>
+      <c r="U73" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="74">
@@ -4638,22 +5525,22 @@
         <v>6.64</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46248.55208333334</v>
+        <v>46251.38541666666</v>
       </c>
       <c r="H74" t="n">
-        <v>401.5</v>
+        <v>399.25</v>
       </c>
       <c r="I74" t="n">
         <v>400.6670800363158</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>14.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K74" t="n">
-        <v>-2.07</v>
+        <v>-2.62</v>
       </c>
       <c r="L74" t="n">
-        <v>3.39</v>
+        <v>3.78</v>
       </c>
       <c r="M74" t="n">
         <v>0.95</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,19 +5594,19 @@
         <v>3.99</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46282.55208333334</v>
+        <v>46283.38541666666</v>
       </c>
       <c r="H75" t="n">
-        <v>390.15</v>
+        <v>401.85</v>
       </c>
       <c r="I75" t="n">
         <v>399.4146651124296</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>32</v>
       </c>
       <c r="K75" t="n">
-        <v>2.28</v>
+        <v>-0.65</v>
       </c>
       <c r="L75" t="n">
         <v>4.31</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>2</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,22 +5663,22 @@
         <v>6.22</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46290.55208333334</v>
+        <v>46293.38541666666</v>
       </c>
       <c r="H76" t="n">
-        <v>390.75</v>
+        <v>382.15</v>
       </c>
       <c r="I76" t="n">
         <v>385.6849187396868</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>10</v>
       </c>
       <c r="K76" t="n">
-        <v>-2.76</v>
+        <v>-4.9</v>
       </c>
       <c r="L76" t="n">
-        <v>4.24</v>
+        <v>5.24</v>
       </c>
       <c r="M76" t="n">
         <v>1.82</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S76" t="b">
+        <v>0</v>
+      </c>
+      <c r="T76" t="n">
+        <v>1</v>
+      </c>
+      <c r="U76" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="77">
@@ -4833,6 +5756,14 @@
       <c r="Q77" t="n">
         <v>40</v>
       </c>
+      <c r="R77" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S77" t="b">
+        <v>1</v>
+      </c>
+      <c r="T77" t="inlineStr"/>
+      <c r="U77" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6935,7 +7866,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="6">
@@ -6945,7 +7876,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>19.2</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7">
@@ -6955,7 +7886,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>75.8</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8">
@@ -6965,7 +7896,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6975,7 +7906,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>31.1</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10">
@@ -6985,7 +7916,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>39.6</v>
+        <v>40</v>
       </c>
     </row>
     <row r="11">
@@ -6995,7 +7926,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12">
@@ -7005,7 +7936,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="13">
@@ -7015,7 +7946,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>70.7</v>
+        <v>69.3</v>
       </c>
     </row>
     <row r="14">
@@ -7025,7 +7956,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.74</v>
+        <v>-1.01</v>
       </c>
     </row>
     <row r="15">
@@ -7035,7 +7966,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3.77</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="16">
@@ -7045,7 +7976,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-0.34</v>
+        <v>-2.75</v>
       </c>
     </row>
     <row r="17">
@@ -7055,7 +7986,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>32.91</v>
+        <v>31.22</v>
       </c>
     </row>
     <row r="18">
@@ -7065,7 +7996,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>41.3</v>
+        <v>30.7</v>
       </c>
     </row>
     <row r="19">
@@ -7075,7 +8006,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.33</v>
+        <v>5.3</v>
       </c>
     </row>
     <row r="20">
@@ -7085,7 +8016,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.15</v>
+        <v>4.57</v>
       </c>
     </row>
     <row r="21">
@@ -7095,7 +8026,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>13.02</v>
+        <v>15.09</v>
       </c>
     </row>
     <row r="22">
@@ -7105,7 +8036,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>21</v>
+        <v>32</v>
       </c>
     </row>
     <row r="23">
@@ -7115,7 +8046,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="24">
@@ -7125,7 +8056,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.3</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="25">
@@ -7135,7 +8066,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.74</v>
+        <v>10.33</v>
       </c>
     </row>
     <row r="26">
@@ -7145,7 +8076,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.33</v>
+        <v>4.28</v>
       </c>
     </row>
     <row r="27">
@@ -7155,7 +8086,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>7.47</v>
+        <v>11.9</v>
       </c>
     </row>
     <row r="28">
@@ -7165,7 +8096,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>17</v>
+        <v>31</v>
       </c>
     </row>
     <row r="29">
